--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101558408</v>
+        <v>1997479</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O Lilla Brassberget, Brassberget, Ramsjö, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538701.0015197303</v>
+        <v>538786.1884826859</v>
       </c>
       <c r="R2" t="n">
-        <v>6897265.578997525</v>
+        <v>6896930.050544007</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -767,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -775,11 +763,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Adult som varnar intensivt alldeles intill ett nyupphackat hål i asp som står i vägkanten (NO om vägen). Passerade platsen två gånger under dagen och varnande på samma ställe både gångerna. Tyder på häckning. Inget tiggläte hördes.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,26 +771,40 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Sälg 20 cm</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Persson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Persson, Cecilia Lindén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107569727</v>
+        <v>909822</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,37 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538666.4771051508</v>
+        <v>538786.1884826859</v>
       </c>
       <c r="R3" t="n">
-        <v>6897219.445653901</v>
+        <v>6896930.050544007</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,30 +897,44 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sälg 20 cm</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107569723</v>
+        <v>1997480</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
+        <v>78569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -932,42 +943,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538701</v>
+        <v>538949.1370083849</v>
       </c>
       <c r="R4" t="n">
-        <v>6897269</v>
+        <v>6896865.184479981</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,22 +1001,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,26 +1027,40 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövrik tallskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg 15 cm</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107569712</v>
+        <v>1936814</v>
       </c>
       <c r="B5" t="n">
-        <v>89376</v>
+        <v>78602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,37 +1073,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538885.9762778704</v>
+        <v>538786.1884826859</v>
       </c>
       <c r="R5" t="n">
-        <v>6896870.056123183</v>
+        <v>6896930.050544007</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1127,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,74 +1153,83 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sälg 20 cm</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107569724</v>
+        <v>2072911</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
+        <v>78596</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538717</v>
+        <v>538949.1370083849</v>
       </c>
       <c r="R6" t="n">
-        <v>6897250</v>
+        <v>6896865.184479981</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1253,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,26 +1279,40 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sälg 15 cm</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107569716</v>
+        <v>3066358</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
+        <v>96334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,46 +1321,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538655.1697634895</v>
+        <v>538769.0790793492</v>
       </c>
       <c r="R7" t="n">
-        <v>6896942.080684811</v>
+        <v>6897035.803612311</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,22 +1379,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,26 +1405,40 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Intill liten bäck</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107569721</v>
+        <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
+        <v>96237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,41 +1447,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>S Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538177.4376702965</v>
+        <v>538435.8017539075</v>
       </c>
       <c r="R8" t="n">
-        <v>6897315.142657178</v>
+        <v>6897036.652886739</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,24 +1503,29 @@
           <t>Ramsjö</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>PST199108081859</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>1991-08-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>1991-08-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,26 +1536,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Björn Wannberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107569733</v>
+        <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>76909</v>
+        <v>96254</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,41 +1573,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>S Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538719.2812472982</v>
+        <v>538435.8017539075</v>
       </c>
       <c r="R9" t="n">
-        <v>6897017.028415164</v>
+        <v>6897036.652886739</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,24 +1625,29 @@
           <t>Ramsjö</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>PST199108081859</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>1991-08-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>1991-08-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,30 +1658,39 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Björn Wannberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107569726</v>
+        <v>101558408</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
+        <v>56395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1619,34 +1699,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>O Lilla Brassberget, Brassberget, Ramsjö, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538663.683839104</v>
+        <v>538701.0015197303</v>
       </c>
       <c r="R10" t="n">
-        <v>6897218.480186098</v>
+        <v>6897265.578997525</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,22 +1765,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Adult som varnar intensivt alldeles intill ett nyupphackat hål i asp som står i vägkanten (NO om vägen). Passerade platsen två gånger under dagen och varnande på samma ställe både gångerna. Tyder på häckning. Inget tiggläte hördes.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,15 +1800,1939 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Persson, Cecilia Lindén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107569713</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78602</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>538783.395008387</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6896929.08489732</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Isak Vahlström, Aron Dynesius</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>107569729</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77259</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538592.8435302821</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6897037.514397588</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>107569727</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>538666.4771051508</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6897219.445653901</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107569723</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57265</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>538701</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6897269</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107569735</v>
+      </c>
+      <c r="B15" t="n">
+        <v>77259</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>538756.8741789052</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6897040.330533164</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>107569738</v>
+      </c>
+      <c r="B16" t="n">
+        <v>76909</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>538754.0217491618</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6897044.498310538</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>107569715</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78570</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>538781.0742731357</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6896927.65794572</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>107569712</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89376</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>538885.9762778704</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6896870.056123183</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107569724</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57265</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>538717</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6897250</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>107569716</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56411</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>538655.1697634895</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6896942.080684811</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>107569721</v>
+      </c>
+      <c r="B21" t="n">
+        <v>77259</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>538177.4376702965</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6897315.142657178</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>107569730</v>
+      </c>
+      <c r="B22" t="n">
+        <v>77258</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>538590.0394034884</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6897037.482282482</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>107569733</v>
+      </c>
+      <c r="B23" t="n">
+        <v>76909</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>538719.2812472982</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6897017.028415164</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107569736</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56411</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>538765.7539075841</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6897040.432678683</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>107569726</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>538663.683839104</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6897218.480186098</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>107569714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>538782.4387848524</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6896930.940880943</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>107569718</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78503</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>538611.6799613461</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6896984.5223502</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,12 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538435.8017539075</v>
+        <v>538436</v>
       </c>
       <c r="R8" t="n">
-        <v>6897036.652886739</v>
+        <v>6897037</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1513,19 +1508,9 @@
           <t>1991-08-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1991-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,12 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538435.8017539075</v>
+        <v>538436</v>
       </c>
       <c r="R9" t="n">
-        <v>6897036.652886739</v>
+        <v>6897037</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1635,19 +1615,9 @@
           <t>1991-08-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1991-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -1438,7 +1438,7 @@
         <v>84213055</v>
       </c>
       <c r="B8" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>84213054</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1997479</v>
+        <v>909822</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538786.1884826859</v>
+        <v>538786</v>
       </c>
       <c r="R2" t="n">
-        <v>6896930.050544007</v>
+        <v>6896930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2012-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>909822</v>
+        <v>107569715</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538786.1884826859</v>
+        <v>538781</v>
       </c>
       <c r="R3" t="n">
-        <v>6896930.050544007</v>
+        <v>6896928</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,87 +877,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövbränna</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg 20 cm</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1997480</v>
+        <v>107569712</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538949.1370083849</v>
+        <v>538886</v>
       </c>
       <c r="R4" t="n">
-        <v>6896865.184479981</v>
+        <v>6896870</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,83 +984,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövrik tallskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälg 15 cm</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1936814</v>
+        <v>107569733</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538786.1884826859</v>
+        <v>538719</v>
       </c>
       <c r="R5" t="n">
-        <v>6896930.050544007</v>
+        <v>6897017</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,83 +1091,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövbränna</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sälg 20 cm</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2072911</v>
+        <v>107569738</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538949.1370083849</v>
+        <v>538754</v>
       </c>
       <c r="R6" t="n">
-        <v>6896865.184479981</v>
+        <v>6897044</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,22 +1172,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,83 +1198,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Sälg 15 cm</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3066358</v>
+        <v>107569730</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538769.0790793492</v>
+        <v>538590</v>
       </c>
       <c r="R7" t="n">
-        <v>6897035.803612311</v>
+        <v>6897038</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1279,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-09-26</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,40 +1305,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövbränna</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Intill liten bäck</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84213055</v>
+        <v>107569718</v>
       </c>
       <c r="B8" t="n">
-        <v>98563</v>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,37 +1332,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Brassbergsmyran, Hls</t>
+          <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538436</v>
+        <v>538611</v>
       </c>
       <c r="R8" t="n">
-        <v>6897037</v>
+        <v>6896985</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,19 +1384,24 @@
           <t>Ramsjö</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>PST199108081859</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1991-08-08</t>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1991-08-08</t>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,69 +1412,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84213054</v>
+        <v>1997478</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Brassbergsmyran, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538436</v>
+        <v>538763</v>
       </c>
       <c r="R9" t="n">
-        <v>6897037</v>
+        <v>6896978</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,19 +1491,19 @@
           <t>Ramsjö</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>PST199108081859</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1991-08-08</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1991-08-08</t>
+          <t>2012-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,37 +1517,37 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Fattigkärr</t>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Aspstubbar och sälglågor</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Hälsinglands flora (2019)</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101558408</v>
+        <v>1997479</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,49 +1555,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O Lilla Brassberget, Brassberget, Ramsjö, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538701.0015197303</v>
+        <v>538786</v>
       </c>
       <c r="R10" t="n">
-        <v>6897265.578997525</v>
+        <v>6896930</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,27 +1609,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Adult som varnar intensivt alldeles intill ett nyupphackat hål i asp som står i vägkanten (NO om vägen). Passerade platsen två gånger under dagen och varnande på samma ställe både gångerna. Tyder på häckning. Inget tiggläte hördes.</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,69 +1625,82 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälg 20 cm</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Persson</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Persson, Cecilia Lindén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107569713</v>
+        <v>1997480</v>
       </c>
       <c r="B11" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538783.395008387</v>
+        <v>538949</v>
       </c>
       <c r="R11" t="n">
-        <v>6896929.08489732</v>
+        <v>6896865</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1852,22 +1724,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,31 +1740,40 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövrik tallskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sälg 15 cm</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107569729</v>
+        <v>107569714</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538592.8435302821</v>
+        <v>538782</v>
       </c>
       <c r="R12" t="n">
-        <v>6897037.514397588</v>
+        <v>6896931</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1969,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,15 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107569727</v>
+        <v>107569726</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538666.4771051508</v>
+        <v>538664</v>
       </c>
       <c r="R13" t="n">
-        <v>6897219.445653901</v>
+        <v>6897218</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2081,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,15 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107569723</v>
+        <v>107569727</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,39 +1995,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538701</v>
+        <v>538667</v>
       </c>
       <c r="R14" t="n">
-        <v>6897269</v>
+        <v>6897219</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2198,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,53 +2091,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107569735</v>
+        <v>2072911</v>
       </c>
       <c r="B15" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538756.8741789052</v>
+        <v>538949</v>
       </c>
       <c r="R15" t="n">
-        <v>6897040.330533164</v>
+        <v>6896865</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2305,22 +2156,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,69 +2172,78 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sälg 15 cm</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107569738</v>
+        <v>1936814</v>
       </c>
       <c r="B16" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538754.0217491618</v>
+        <v>538786</v>
       </c>
       <c r="R16" t="n">
-        <v>6897044.498310538</v>
+        <v>6896930</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,22 +2267,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,53 +2283,62 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Sälg 20 cm</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107569715</v>
+        <v>107569713</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2499,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538781.0742731357</v>
+        <v>538783</v>
       </c>
       <c r="R17" t="n">
-        <v>6896927.65794572</v>
+        <v>6896929</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2534,7 +2383,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2393,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,37 +2420,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107569712</v>
+        <v>107569737</v>
       </c>
       <c r="B18" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4660</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2611,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538885.9762778704</v>
+        <v>538758</v>
       </c>
       <c r="R18" t="n">
-        <v>6896870.056123183</v>
+        <v>6897050</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2646,7 +2490,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2500,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,32 +2527,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107569724</v>
+        <v>107569716</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2719,7 +2558,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2728,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538717</v>
+        <v>538655</v>
       </c>
       <c r="R19" t="n">
-        <v>6897250</v>
+        <v>6896942</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2763,7 +2602,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2612,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,19 +2639,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107569716</v>
+        <v>107569736</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2845,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538655.1697634895</v>
+        <v>538766</v>
       </c>
       <c r="R20" t="n">
-        <v>6896942.080684811</v>
+        <v>6897041</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2880,7 +2714,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2890,7 +2724,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2917,15 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107569721</v>
+        <v>101558408</v>
       </c>
       <c r="B21" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,34 +2762,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>O Lilla Brassberget, Brassberget, Ramsjö, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538177.4376702965</v>
+        <v>538701</v>
       </c>
       <c r="R21" t="n">
-        <v>6897315.142657178</v>
+        <v>6897266</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2987,22 +2828,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Adult som varnar intensivt alldeles intill ett nyupphackat hål i asp som står i vägkanten (NO om vägen). Passerade platsen två gånger under dagen och varnande på samma ställe både gångerna. Tyder på häckning. Inget tiggläte hördes.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,27 +2853,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Helena Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
+          <t>Helena Persson, Cecilia Lindén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107569730</v>
+        <v>107569723</v>
       </c>
       <c r="B22" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,34 +2876,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538590.0394034884</v>
+        <v>538701</v>
       </c>
       <c r="R22" t="n">
-        <v>6897037.482282482</v>
+        <v>6897269</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3104,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3114,7 +2950,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,15 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107569733</v>
+        <v>107569724</v>
       </c>
       <c r="B23" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,34 +2988,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538719.2812472982</v>
+        <v>538717</v>
       </c>
       <c r="R23" t="n">
-        <v>6897017.028415164</v>
+        <v>6897250</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3216,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3226,7 +3062,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3253,43 +3089,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107569736</v>
+        <v>107569719</v>
       </c>
       <c r="B24" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3298,10 +3129,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538765.7539075841</v>
+        <v>538486</v>
       </c>
       <c r="R24" t="n">
-        <v>6897040.432678683</v>
+        <v>6897089</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3333,7 +3164,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3343,7 +3174,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3370,50 +3201,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107569726</v>
+        <v>107569720</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brassberget, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538663.683839104</v>
+        <v>538377</v>
       </c>
       <c r="R25" t="n">
-        <v>6897218.480186098</v>
+        <v>6897175</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3445,7 +3276,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,7 +3286,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,53 +3313,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107569714</v>
+        <v>3066358</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brassberget, Hls</t>
+          <t>Brassbergsmyran, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538782.4387848524</v>
+        <v>538769</v>
       </c>
       <c r="R26" t="n">
-        <v>6896930.940880943</v>
+        <v>6897036</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3552,22 +3378,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:16</t>
+          <t>2012-09-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,53 +3394,62 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Intill liten bäck</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Aron Dynesius</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107569718</v>
+        <v>107569721</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3634,10 +3459,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538611.6799613461</v>
+        <v>538178</v>
       </c>
       <c r="R27" t="n">
-        <v>6896984.5223502</v>
+        <v>6897315</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3669,7 +3494,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3504,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3703,6 +3528,220 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>107569729</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>538593</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6897038</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>107569735</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brassberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>538757</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6897041</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18631-2022 artfynd.xlsx
+++ b/artfynd/A 18631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/909822</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569712</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569733</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569738</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569730</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569718</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997478</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997479</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997480</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569714</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569726</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2419,6 +2499,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569727</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072911</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,6 +2731,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1936814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2748,6 +2843,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569713</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2855,6 +2955,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569737</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2967,6 +3072,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569716</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3079,6 +3189,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569736</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101558408</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3305,6 +3425,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569723</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569724</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3528,6 +3658,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3066358</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3635,6 +3770,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569729</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3742,8 +3882,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>